--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:33</t>
+    <t xml:space="preserve">2026-10-04 09:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:03</t>
+    <t xml:space="preserve">2026-10-05 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -779,7 +779,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>356060.62</v>
+        <v>356060.63</v>
       </c>
     </row>
     <row r="14">
@@ -932,7 +932,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>312231.62</v>
+        <v>312231.63</v>
       </c>
     </row>
     <row r="23">
@@ -1102,7 +1102,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>264802.12</v>
+        <v>264802.13</v>
       </c>
     </row>
     <row r="33">
